--- a/xls/square_16_tri3_14.xlsx
+++ b/xls/square_16_tri3_14.xlsx
@@ -482,13 +482,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>1.2330882887227261</v>
+        <v>1.2330883610868444</v>
       </c>
       <c r="J14">
-        <v>-1.5575919986405504</v>
+        <v>-1.5575919281942072</v>
       </c>
       <c r="K14">
-        <v>-0.22899843051970262</v>
+        <v>-0.2289983906139322</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.3424264776731487</v>
+        <v>-2.3424263003789823</v>
       </c>
       <c r="J15">
-        <v>-2.102974781517326</v>
+        <v>-2.102974601254045</v>
       </c>
       <c r="K15">
-        <v>-1.5392834240903874</v>
+        <v>-1.5392834640897315</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.3343654473268267</v>
+        <v>-2.3343654725473217</v>
       </c>
       <c r="J16">
-        <v>-2.0989585112807583</v>
+        <v>-2.098958040776307</v>
       </c>
       <c r="K16">
-        <v>-1.6105066655047886</v>
+        <v>-1.6105066983182497</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-2.3204471354043146</v>
+        <v>-2.3204485873768026</v>
       </c>
       <c r="J17">
-        <v>-2.1011235260988834</v>
+        <v>-2.101123244202551</v>
       </c>
       <c r="K17">
-        <v>0.9007116991930865</v>
+        <v>0.9007126015899933</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-2.3016663640625885</v>
+        <v>-2.3016667009382936</v>
       </c>
       <c r="J18">
-        <v>-1.9509937625528693</v>
+        <v>-1.950993937475886</v>
       </c>
       <c r="K18">
-        <v>0.6924465904551657</v>
+        <v>0.6924466281597436</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-2.0180101826633585</v>
+        <v>-2.018010699210582</v>
       </c>
       <c r="J19">
-        <v>-1.5758319970561483</v>
+        <v>-1.57583212263745</v>
       </c>
       <c r="K19">
-        <v>2.989333052190855</v>
+        <v>2.9893330773934816</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.6311186461042662</v>
+        <v>-0.6311186222022926</v>
       </c>
       <c r="J20">
-        <v>-0.5454663702501286</v>
+        <v>-0.5454663604025792</v>
       </c>
       <c r="K20">
-        <v>3.8409636474530546</v>
+        <v>3.840963647100463</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.11843091523740051</v>
+        <v>-0.11843091486306237</v>
       </c>
       <c r="J21">
-        <v>-0.10423082181909916</v>
+        <v>-0.10423082163569446</v>
       </c>
       <c r="K21">
-        <v>3.846165337470628</v>
+        <v>3.8461653376295297</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.01663185551793631</v>
+        <v>-0.016631855368581135</v>
       </c>
       <c r="J22">
-        <v>-0.016516325087489275</v>
+        <v>-0.016516325038555518</v>
       </c>
       <c r="K22">
-        <v>3.544067688961228</v>
+        <v>3.544067690504438</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0008242802001466694</v>
+        <v>-0.000824280202340576</v>
       </c>
       <c r="J23">
-        <v>-0.000560215705547165</v>
+        <v>-0.0005602157068880551</v>
       </c>
       <c r="K23">
-        <v>2.6450395614246163</v>
+        <v>2.6450395622197047</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.0004069246943975239</v>
+        <v>-0.000406924694230201</v>
       </c>
       <c r="J24">
-        <v>-0.00032029847316240385</v>
+        <v>-0.0003202984730481915</v>
       </c>
       <c r="K24">
-        <v>2.613052913306231</v>
+        <v>2.613052913015681</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.00012042154442020222</v>
+        <v>-0.00012042154442381945</v>
       </c>
       <c r="J25">
-        <v>-9.122295833613228e-5</v>
+        <v>-9.122295833849538e-5</v>
       </c>
       <c r="K25">
-        <v>2.3519976188585807</v>
+        <v>2.351997618764341</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.0003986635809382055</v>
+        <v>-0.0003986635808786036</v>
       </c>
       <c r="J26">
-        <v>-0.00031914657251306877</v>
+        <v>-0.0003191465724700764</v>
       </c>
       <c r="K26">
-        <v>2.6233016335864323</v>
+        <v>2.623301633574335</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -937,13 +937,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>2.5000504553243764e-5</v>
+        <v>2.5000504550543802e-5</v>
       </c>
       <c r="J27">
-        <v>5.672660288410276e-6</v>
+        <v>5.672660287638825e-6</v>
       </c>
       <c r="K27">
-        <v>2.0693409372384868</v>
+        <v>2.069340937373347</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-4.828311769511966e-5</v>
+        <v>-4.82831176852342e-5</v>
       </c>
       <c r="J28">
-        <v>-2.95770723757421e-5</v>
+        <v>-2.9577072369907523e-5</v>
       </c>
       <c r="K28">
-        <v>1.902553809925243</v>
+        <v>1.9025538099028627</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-9.196741409555389e-8</v>
+        <v>-9.196741414377028e-8</v>
       </c>
       <c r="J29">
         <v>-2.1933102931832556e-7</v>
       </c>
       <c r="K29">
-        <v>1.2362756990977741</v>
+        <v>1.2362756991444697</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-5.422811158276041e-7</v>
+        <v>-5.422811156347384e-7</v>
       </c>
       <c r="J30">
-        <v>-4.565313586133233e-7</v>
+        <v>-4.565313585651069e-7</v>
       </c>
       <c r="K30">
-        <v>1.2304457913010427</v>
+        <v>1.2304457913748248</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-7.636027251606779e-7</v>
+        <v>-7.636027251124615e-7</v>
       </c>
       <c r="J31">
-        <v>-5.575996600125633e-7</v>
+        <v>-5.575996601572126e-7</v>
       </c>
       <c r="K31">
-        <v>1.2151622262297332</v>
+        <v>1.2151622263871642</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-3.585412962880253e-7</v>
+        <v>-3.585412962398089e-7</v>
       </c>
       <c r="J32">
-        <v>-3.1760871084100967e-7</v>
+        <v>-3.1760871093744247e-7</v>
       </c>
       <c r="K32">
-        <v>1.1691364838541696</v>
+        <v>1.1691364836563563</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_14.xlsx
+++ b/xls/square_16_tri3_14.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>289</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>4.383202952177157</v>
+      </c>
+      <c r="J12">
+        <v>0.6869507380889515</v>
+      </c>
+      <c r="K12">
+        <v>1.5006591743505002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>3.1822503670893676</v>
+      </c>
+      <c r="J13">
+        <v>-0.15977084326021282</v>
+      </c>
+      <c r="K13">
+        <v>0.8871803243962942</v>
+      </c>
+    </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>

--- a/xls/square_16_tri3_14.xlsx
+++ b/xls/square_16_tri3_14.xlsx
@@ -482,13 +482,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.410653275070715</v>
+        <v>-2.4032502046224637</v>
       </c>
       <c r="J16">
-        <v>-2.0340185439290073</v>
+        <v>-2.0297930433393114</v>
       </c>
       <c r="K16">
-        <v>-1.5929176336602466</v>
+        <v>-1.5939374611557813</v>
       </c>
     </row>
   </sheetData>
